--- a/スケジュール.xlsx
+++ b/スケジュール.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2590345_黒沢爽次\チーム制作\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\川上 紗英\チーム制作\GameProductionPractice1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAEC291-AC69-4C9C-A4B8-4009FFA5CAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687086A4-E66A-400C-9910-B253611BEC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="1935" windowWidth="21600" windowHeight="11295" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="630" yWindow="-12525" windowWidth="21600" windowHeight="11295" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>2月</t>
     <rPh sb="1" eb="2">
@@ -74,16 +74,43 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>久野</t>
+    <t>馬場</t>
     <rPh sb="0" eb="2">
-      <t>クノ</t>
+      <t>ババ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>馬場</t>
-    <rPh sb="0" eb="2">
-      <t>ババ</t>
+    <t>マップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タイトル、オプション、セーブ、ロード画面、敵の動き</t>
+    <rPh sb="18" eb="20">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プレイヤーの動き</t>
+    <rPh sb="6" eb="7">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>工野</t>
+    <rPh sb="0" eb="1">
+      <t>タクミ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ノ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -147,7 +174,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -211,13 +238,99 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -252,6 +365,33 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -780,21 +920,23 @@
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="9"/>
-      <c r="AB3" s="9"/>
+      <c r="N3" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="17"/>
       <c r="AC3" s="9"/>
       <c r="AD3" s="9"/>
       <c r="AE3" s="9"/>
@@ -830,7 +972,7 @@
     </row>
     <row r="4" spans="1:60" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -844,21 +986,21 @@
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
-      <c r="AB4" s="9"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19"/>
+      <c r="Y4" s="19"/>
+      <c r="Z4" s="19"/>
+      <c r="AA4" s="19"/>
+      <c r="AB4" s="20"/>
       <c r="AC4" s="9"/>
       <c r="AD4" s="9"/>
       <c r="AE4" s="9"/>
@@ -908,21 +1050,23 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="9"/>
+      <c r="N5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="13"/>
+      <c r="AB5" s="14"/>
       <c r="AC5" s="9"/>
       <c r="AD5" s="9"/>
       <c r="AE5" s="9"/>
@@ -958,7 +1102,7 @@
     </row>
     <row r="6" spans="1:60" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A6" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -972,21 +1116,23 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
+      <c r="N6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="14"/>
       <c r="AC6" s="9"/>
       <c r="AD6" s="9"/>
       <c r="AE6" s="9"/>
@@ -1026,6 +1172,11 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="N6:AB6"/>
+    <mergeCell ref="N5:AB5"/>
+    <mergeCell ref="N3:AB4"/>
+  </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1033,6 +1184,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -1227,17 +1389,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1248,6 +1399,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1266,17 +1428,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
   <ds:schemaRefs>

--- a/スケジュール.xlsx
+++ b/スケジュール.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\川上 紗英\チーム制作\GameProductionPractice1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2590345_黒沢爽次\チーム制作\GitHub\GameProductionPractice1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687086A4-E66A-400C-9910-B253611BEC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{520A1F93-691E-43BE-852D-22C4A43E4AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="-12525" windowWidth="21600" windowHeight="11295" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="4185" yWindow="-14235" windowWidth="21600" windowHeight="11370" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>2月</t>
     <rPh sb="1" eb="2">
@@ -81,23 +81,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>マップ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>タイトル、オプション、セーブ、ロード画面、敵の動き</t>
-    <rPh sb="18" eb="20">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ウゴ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>プレイヤーの動き</t>
     <rPh sb="6" eb="7">
       <t>ウゴ</t>
@@ -111,6 +94,49 @@
     </rPh>
     <rPh sb="1" eb="2">
       <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ギミック</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮マップ</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>セーブ・ロード</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>不具合修正</t>
+    <rPh sb="0" eb="3">
+      <t>フグアイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マップ制作</t>
+    <rPh sb="3" eb="5">
+      <t>セイサク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -174,7 +200,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -324,13 +350,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -373,6 +417,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -392,6 +442,39 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -920,42 +1003,46 @@
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
-      <c r="N3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
-      <c r="T3" s="16"/>
-      <c r="U3" s="16"/>
-      <c r="V3" s="16"/>
-      <c r="W3" s="16"/>
-      <c r="X3" s="16"/>
-      <c r="Y3" s="16"/>
-      <c r="Z3" s="16"/>
-      <c r="AA3" s="16"/>
-      <c r="AB3" s="17"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
+      <c r="Y3" s="29"/>
+      <c r="Z3" s="29"/>
+      <c r="AA3" s="29"/>
+      <c r="AB3" s="30"/>
       <c r="AC3" s="9"/>
       <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
+      <c r="AE3" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="AF3" s="9"/>
       <c r="AG3" s="9"/>
       <c r="AH3" s="9"/>
       <c r="AI3" s="9"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="9"/>
-      <c r="AL3" s="9"/>
-      <c r="AM3" s="9"/>
-      <c r="AN3" s="9"/>
-      <c r="AO3" s="9"/>
-      <c r="AP3" s="9"/>
-      <c r="AQ3" s="9"/>
-      <c r="AR3" s="9"/>
-      <c r="AS3" s="9"/>
-      <c r="AT3" s="9"/>
-      <c r="AU3" s="9"/>
+      <c r="AL3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM3" s="18"/>
+      <c r="AN3" s="18"/>
+      <c r="AO3" s="18"/>
+      <c r="AP3" s="18"/>
+      <c r="AQ3" s="18"/>
+      <c r="AR3" s="18"/>
+      <c r="AS3" s="18"/>
+      <c r="AT3" s="18"/>
+      <c r="AU3" s="19"/>
       <c r="AV3" s="9"/>
       <c r="AW3" s="9"/>
       <c r="AX3" s="9"/>
@@ -972,7 +1059,7 @@
     </row>
     <row r="4" spans="1:60" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -986,40 +1073,42 @@
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="20"/>
-      <c r="AC4" s="9"/>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="9"/>
-      <c r="AF4" s="9"/>
-      <c r="AG4" s="9"/>
-      <c r="AH4" s="9"/>
-      <c r="AI4" s="9"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="28"/>
       <c r="AJ4" s="9"/>
       <c r="AK4" s="9"/>
-      <c r="AL4" s="9"/>
-      <c r="AM4" s="9"/>
-      <c r="AN4" s="9"/>
-      <c r="AO4" s="9"/>
-      <c r="AP4" s="9"/>
-      <c r="AQ4" s="9"/>
-      <c r="AR4" s="9"/>
-      <c r="AS4" s="9"/>
-      <c r="AT4" s="9"/>
-      <c r="AU4" s="9"/>
+      <c r="AL4" s="31"/>
+      <c r="AM4" s="32"/>
+      <c r="AN4" s="32"/>
+      <c r="AO4" s="32"/>
+      <c r="AP4" s="32"/>
+      <c r="AQ4" s="32"/>
+      <c r="AR4" s="32"/>
+      <c r="AS4" s="32"/>
+      <c r="AT4" s="32"/>
+      <c r="AU4" s="33"/>
       <c r="AV4" s="9"/>
       <c r="AW4" s="9"/>
       <c r="AX4" s="9"/>
@@ -1050,42 +1139,42 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
-      <c r="N5" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="9"/>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="9"/>
-      <c r="AF5" s="9"/>
-      <c r="AG5" s="9"/>
-      <c r="AH5" s="9"/>
-      <c r="AI5" s="9"/>
+      <c r="N5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15"/>
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" s="15"/>
+      <c r="AC5" s="15"/>
+      <c r="AD5" s="15"/>
+      <c r="AE5" s="15"/>
+      <c r="AF5" s="15"/>
+      <c r="AG5" s="15"/>
+      <c r="AH5" s="15"/>
+      <c r="AI5" s="16"/>
       <c r="AJ5" s="9"/>
       <c r="AK5" s="9"/>
-      <c r="AL5" s="9"/>
-      <c r="AM5" s="9"/>
-      <c r="AN5" s="9"/>
-      <c r="AO5" s="9"/>
-      <c r="AP5" s="9"/>
-      <c r="AQ5" s="9"/>
-      <c r="AR5" s="9"/>
-      <c r="AS5" s="9"/>
-      <c r="AT5" s="9"/>
-      <c r="AU5" s="9"/>
+      <c r="AL5" s="20"/>
+      <c r="AM5" s="21"/>
+      <c r="AN5" s="21"/>
+      <c r="AO5" s="21"/>
+      <c r="AP5" s="21"/>
+      <c r="AQ5" s="21"/>
+      <c r="AR5" s="21"/>
+      <c r="AS5" s="21"/>
+      <c r="AT5" s="21"/>
+      <c r="AU5" s="22"/>
       <c r="AV5" s="9"/>
       <c r="AW5" s="9"/>
       <c r="AX5" s="9"/>
@@ -1116,37 +1205,41 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="12" t="s">
-        <v>6</v>
-      </c>
+      <c r="N6" s="12"/>
       <c r="O6" s="13"/>
       <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
-      <c r="AF6" s="9"/>
-      <c r="AG6" s="9"/>
-      <c r="AH6" s="9"/>
-      <c r="AI6" s="9"/>
+      <c r="Q6" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="15"/>
+      <c r="AC6" s="15"/>
+      <c r="AD6" s="15"/>
+      <c r="AE6" s="15"/>
+      <c r="AF6" s="15"/>
+      <c r="AG6" s="15"/>
+      <c r="AH6" s="15"/>
+      <c r="AI6" s="16"/>
       <c r="AJ6" s="9"/>
       <c r="AK6" s="9"/>
-      <c r="AL6" s="9"/>
-      <c r="AM6" s="9"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="9"/>
-      <c r="AP6" s="9"/>
+      <c r="AL6" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM6" s="15"/>
+      <c r="AN6" s="15"/>
+      <c r="AO6" s="15"/>
+      <c r="AP6" s="16"/>
       <c r="AQ6" s="9"/>
       <c r="AR6" s="9"/>
       <c r="AS6" s="9"/>
@@ -1172,10 +1265,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="N6:AB6"/>
-    <mergeCell ref="N5:AB5"/>
-    <mergeCell ref="N3:AB4"/>
+  <mergeCells count="7">
+    <mergeCell ref="AL3:AU5"/>
+    <mergeCell ref="AL6:AP6"/>
+    <mergeCell ref="N5:AI5"/>
+    <mergeCell ref="S6:AI6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="S3:AB3"/>
+    <mergeCell ref="S4:AI4"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1184,17 +1281,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -1389,6 +1475,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1399,17 +1496,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1428,6 +1514,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
   <ds:schemaRefs>

--- a/スケジュール.xlsx
+++ b/スケジュール.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\川上 紗英\チーム制作\GameProductionPractice1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687086A4-E66A-400C-9910-B253611BEC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB18544-CC6D-4387-919C-00C3715243E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="-12525" windowWidth="21600" windowHeight="11295" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="5565" yWindow="-12855" windowWidth="21600" windowHeight="11370" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>2月</t>
     <rPh sb="1" eb="2">
@@ -81,23 +81,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>マップ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>タイトル、オプション、セーブ、ロード画面、敵の動き</t>
-    <rPh sb="18" eb="20">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ウゴ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>プレイヤーの動き</t>
     <rPh sb="6" eb="7">
       <t>ウゴ</t>
@@ -111,6 +94,45 @@
     </rPh>
     <rPh sb="1" eb="2">
       <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ギミック</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮マップ</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>不具合修正</t>
+    <rPh sb="0" eb="3">
+      <t>フグアイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マップ制作</t>
+    <rPh sb="3" eb="5">
+      <t>セイサク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -174,7 +196,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -324,13 +346,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -373,26 +413,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -920,42 +1008,44 @@
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
-      <c r="N3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
-      <c r="T3" s="16"/>
-      <c r="U3" s="16"/>
-      <c r="V3" s="16"/>
-      <c r="W3" s="16"/>
-      <c r="X3" s="16"/>
-      <c r="Y3" s="16"/>
-      <c r="Z3" s="16"/>
-      <c r="AA3" s="16"/>
-      <c r="AB3" s="17"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
-      <c r="AF3" s="9"/>
-      <c r="AG3" s="9"/>
-      <c r="AH3" s="9"/>
-      <c r="AI3" s="9"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="35"/>
+      <c r="AE3" s="35"/>
+      <c r="AF3" s="35"/>
+      <c r="AG3" s="35"/>
+      <c r="AH3" s="35"/>
+      <c r="AI3" s="36"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="9"/>
-      <c r="AL3" s="9"/>
-      <c r="AM3" s="9"/>
-      <c r="AN3" s="9"/>
-      <c r="AO3" s="9"/>
-      <c r="AP3" s="9"/>
-      <c r="AQ3" s="9"/>
-      <c r="AR3" s="9"/>
-      <c r="AS3" s="9"/>
-      <c r="AT3" s="9"/>
-      <c r="AU3" s="9"/>
+      <c r="AL3" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM3" s="19"/>
+      <c r="AN3" s="19"/>
+      <c r="AO3" s="19"/>
+      <c r="AP3" s="19"/>
+      <c r="AQ3" s="19"/>
+      <c r="AR3" s="19"/>
+      <c r="AS3" s="19"/>
+      <c r="AT3" s="19"/>
+      <c r="AU3" s="20"/>
       <c r="AV3" s="9"/>
       <c r="AW3" s="9"/>
       <c r="AX3" s="9"/>
@@ -972,7 +1062,7 @@
     </row>
     <row r="4" spans="1:60" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -986,40 +1076,42 @@
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="20"/>
-      <c r="AC4" s="9"/>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="9"/>
-      <c r="AF4" s="9"/>
-      <c r="AG4" s="9"/>
-      <c r="AH4" s="9"/>
-      <c r="AI4" s="9"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="30"/>
+      <c r="AA4" s="30"/>
+      <c r="AB4" s="30"/>
+      <c r="AC4" s="30"/>
+      <c r="AD4" s="30"/>
+      <c r="AE4" s="30"/>
+      <c r="AF4" s="30"/>
+      <c r="AG4" s="30"/>
+      <c r="AH4" s="30"/>
+      <c r="AI4" s="31"/>
       <c r="AJ4" s="9"/>
       <c r="AK4" s="9"/>
-      <c r="AL4" s="9"/>
-      <c r="AM4" s="9"/>
-      <c r="AN4" s="9"/>
-      <c r="AO4" s="9"/>
-      <c r="AP4" s="9"/>
-      <c r="AQ4" s="9"/>
-      <c r="AR4" s="9"/>
-      <c r="AS4" s="9"/>
-      <c r="AT4" s="9"/>
-      <c r="AU4" s="9"/>
+      <c r="AL4" s="21"/>
+      <c r="AM4" s="22"/>
+      <c r="AN4" s="22"/>
+      <c r="AO4" s="22"/>
+      <c r="AP4" s="22"/>
+      <c r="AQ4" s="22"/>
+      <c r="AR4" s="22"/>
+      <c r="AS4" s="22"/>
+      <c r="AT4" s="22"/>
+      <c r="AU4" s="23"/>
       <c r="AV4" s="9"/>
       <c r="AW4" s="9"/>
       <c r="AX4" s="9"/>
@@ -1050,42 +1142,44 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
-      <c r="N5" s="12" t="s">
+      <c r="N5" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="32"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="9"/>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="9"/>
-      <c r="AF5" s="9"/>
-      <c r="AG5" s="9"/>
-      <c r="AH5" s="9"/>
-      <c r="AI5" s="9"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="32"/>
+      <c r="AD5" s="32"/>
+      <c r="AE5" s="32"/>
+      <c r="AF5" s="32"/>
+      <c r="AG5" s="32"/>
+      <c r="AH5" s="32"/>
+      <c r="AI5" s="33"/>
       <c r="AJ5" s="9"/>
       <c r="AK5" s="9"/>
-      <c r="AL5" s="9"/>
-      <c r="AM5" s="9"/>
-      <c r="AN5" s="9"/>
-      <c r="AO5" s="9"/>
-      <c r="AP5" s="9"/>
-      <c r="AQ5" s="9"/>
-      <c r="AR5" s="9"/>
-      <c r="AS5" s="9"/>
-      <c r="AT5" s="9"/>
-      <c r="AU5" s="9"/>
+      <c r="AL5" s="24"/>
+      <c r="AM5" s="25"/>
+      <c r="AN5" s="25"/>
+      <c r="AO5" s="25"/>
+      <c r="AP5" s="25"/>
+      <c r="AQ5" s="25"/>
+      <c r="AR5" s="25"/>
+      <c r="AS5" s="25"/>
+      <c r="AT5" s="25"/>
+      <c r="AU5" s="26"/>
       <c r="AV5" s="9"/>
       <c r="AW5" s="9"/>
       <c r="AX5" s="9"/>
@@ -1116,37 +1210,41 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="12" t="s">
-        <v>6</v>
-      </c>
+      <c r="N6" s="12"/>
       <c r="O6" s="13"/>
       <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
-      <c r="AF6" s="9"/>
-      <c r="AG6" s="9"/>
-      <c r="AH6" s="9"/>
-      <c r="AI6" s="9"/>
+      <c r="Q6" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="R6" s="32"/>
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="32"/>
+      <c r="AE6" s="32"/>
+      <c r="AF6" s="32"/>
+      <c r="AG6" s="32"/>
+      <c r="AH6" s="32"/>
+      <c r="AI6" s="33"/>
       <c r="AJ6" s="9"/>
       <c r="AK6" s="9"/>
-      <c r="AL6" s="9"/>
-      <c r="AM6" s="9"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="9"/>
-      <c r="AP6" s="9"/>
+      <c r="AL6" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="29"/>
       <c r="AQ6" s="9"/>
       <c r="AR6" s="9"/>
       <c r="AS6" s="9"/>
@@ -1172,10 +1270,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="N6:AB6"/>
-    <mergeCell ref="N5:AB5"/>
-    <mergeCell ref="N3:AB4"/>
+  <mergeCells count="8">
+    <mergeCell ref="AL3:AU5"/>
+    <mergeCell ref="AL6:AP6"/>
+    <mergeCell ref="S4:AI4"/>
+    <mergeCell ref="Q6:AA6"/>
+    <mergeCell ref="AB6:AI6"/>
+    <mergeCell ref="N5:Z5"/>
+    <mergeCell ref="AA5:AI5"/>
+    <mergeCell ref="S3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1184,6 +1287,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
@@ -1194,7 +1306,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -1389,16 +1501,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1409,7 +1520,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1426,12 +1537,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/スケジュール.xlsx
+++ b/スケジュール.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\川上 紗英\チーム制作\GameProductionPractice1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB18544-CC6D-4387-919C-00C3715243E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687086A4-E66A-400C-9910-B253611BEC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5565" yWindow="-12855" windowWidth="21600" windowHeight="11370" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="630" yWindow="-12525" windowWidth="21600" windowHeight="11295" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>2月</t>
     <rPh sb="1" eb="2">
@@ -81,6 +81,23 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>マップ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タイトル、オプション、セーブ、ロード画面、敵の動き</t>
+    <rPh sb="18" eb="20">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ウゴ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>プレイヤーの動き</t>
     <rPh sb="6" eb="7">
       <t>ウゴ</t>
@@ -94,45 +111,6 @@
     </rPh>
     <rPh sb="1" eb="2">
       <t>ノ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ギミック</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>仮マップ</t>
-    <rPh sb="0" eb="1">
-      <t>カリ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>敵</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>タイトル</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>不具合修正</t>
-    <rPh sb="0" eb="3">
-      <t>フグアイ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シュウセイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>マップ制作</t>
-    <rPh sb="3" eb="5">
-      <t>セイサク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -196,7 +174,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -346,31 +324,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -413,16 +373,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
@@ -434,15 +385,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -451,36 +393,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1008,44 +920,42 @@
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="15"/>
-      <c r="S3" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="35"/>
-      <c r="Z3" s="35"/>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="35"/>
-      <c r="AC3" s="35"/>
-      <c r="AD3" s="35"/>
-      <c r="AE3" s="35"/>
-      <c r="AF3" s="35"/>
-      <c r="AG3" s="35"/>
-      <c r="AH3" s="35"/>
-      <c r="AI3" s="36"/>
+      <c r="N3" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="9"/>
-      <c r="AL3" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="AM3" s="19"/>
-      <c r="AN3" s="19"/>
-      <c r="AO3" s="19"/>
-      <c r="AP3" s="19"/>
-      <c r="AQ3" s="19"/>
-      <c r="AR3" s="19"/>
-      <c r="AS3" s="19"/>
-      <c r="AT3" s="19"/>
-      <c r="AU3" s="20"/>
+      <c r="AL3" s="9"/>
+      <c r="AM3" s="9"/>
+      <c r="AN3" s="9"/>
+      <c r="AO3" s="9"/>
+      <c r="AP3" s="9"/>
+      <c r="AQ3" s="9"/>
+      <c r="AR3" s="9"/>
+      <c r="AS3" s="9"/>
+      <c r="AT3" s="9"/>
+      <c r="AU3" s="9"/>
       <c r="AV3" s="9"/>
       <c r="AW3" s="9"/>
       <c r="AX3" s="9"/>
@@ -1062,7 +972,7 @@
     </row>
     <row r="4" spans="1:60" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1076,42 +986,40 @@
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="T4" s="30"/>
-      <c r="U4" s="30"/>
-      <c r="V4" s="30"/>
-      <c r="W4" s="30"/>
-      <c r="X4" s="30"/>
-      <c r="Y4" s="30"/>
-      <c r="Z4" s="30"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
-      <c r="AD4" s="30"/>
-      <c r="AE4" s="30"/>
-      <c r="AF4" s="30"/>
-      <c r="AG4" s="30"/>
-      <c r="AH4" s="30"/>
-      <c r="AI4" s="31"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19"/>
+      <c r="Y4" s="19"/>
+      <c r="Z4" s="19"/>
+      <c r="AA4" s="19"/>
+      <c r="AB4" s="20"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+      <c r="AF4" s="9"/>
+      <c r="AG4" s="9"/>
+      <c r="AH4" s="9"/>
+      <c r="AI4" s="9"/>
       <c r="AJ4" s="9"/>
       <c r="AK4" s="9"/>
-      <c r="AL4" s="21"/>
-      <c r="AM4" s="22"/>
-      <c r="AN4" s="22"/>
-      <c r="AO4" s="22"/>
-      <c r="AP4" s="22"/>
-      <c r="AQ4" s="22"/>
-      <c r="AR4" s="22"/>
-      <c r="AS4" s="22"/>
-      <c r="AT4" s="22"/>
-      <c r="AU4" s="23"/>
+      <c r="AL4" s="9"/>
+      <c r="AM4" s="9"/>
+      <c r="AN4" s="9"/>
+      <c r="AO4" s="9"/>
+      <c r="AP4" s="9"/>
+      <c r="AQ4" s="9"/>
+      <c r="AR4" s="9"/>
+      <c r="AS4" s="9"/>
+      <c r="AT4" s="9"/>
+      <c r="AU4" s="9"/>
       <c r="AV4" s="9"/>
       <c r="AW4" s="9"/>
       <c r="AX4" s="9"/>
@@ -1142,44 +1050,42 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
-      <c r="N5" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="32"/>
-      <c r="S5" s="32"/>
-      <c r="T5" s="32"/>
-      <c r="U5" s="32"/>
-      <c r="V5" s="32"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="32"/>
-      <c r="Y5" s="32"/>
-      <c r="Z5" s="32"/>
-      <c r="AA5" s="32" t="s">
+      <c r="N5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="AB5" s="32"/>
-      <c r="AC5" s="32"/>
-      <c r="AD5" s="32"/>
-      <c r="AE5" s="32"/>
-      <c r="AF5" s="32"/>
-      <c r="AG5" s="32"/>
-      <c r="AH5" s="32"/>
-      <c r="AI5" s="33"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="13"/>
+      <c r="Z5" s="13"/>
+      <c r="AA5" s="13"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+      <c r="AF5" s="9"/>
+      <c r="AG5" s="9"/>
+      <c r="AH5" s="9"/>
+      <c r="AI5" s="9"/>
       <c r="AJ5" s="9"/>
       <c r="AK5" s="9"/>
-      <c r="AL5" s="24"/>
-      <c r="AM5" s="25"/>
-      <c r="AN5" s="25"/>
-      <c r="AO5" s="25"/>
-      <c r="AP5" s="25"/>
-      <c r="AQ5" s="25"/>
-      <c r="AR5" s="25"/>
-      <c r="AS5" s="25"/>
-      <c r="AT5" s="25"/>
-      <c r="AU5" s="26"/>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
       <c r="AV5" s="9"/>
       <c r="AW5" s="9"/>
       <c r="AX5" s="9"/>
@@ -1210,41 +1116,37 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="12"/>
+      <c r="N6" s="12" t="s">
+        <v>6</v>
+      </c>
       <c r="O6" s="13"/>
       <c r="P6" s="13"/>
-      <c r="Q6" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="R6" s="32"/>
-      <c r="S6" s="32"/>
-      <c r="T6" s="32"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="32"/>
-      <c r="W6" s="32"/>
-      <c r="X6" s="32"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="32"/>
-      <c r="AB6" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="32"/>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="32"/>
-      <c r="AG6" s="32"/>
-      <c r="AH6" s="32"/>
-      <c r="AI6" s="33"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+      <c r="AF6" s="9"/>
+      <c r="AG6" s="9"/>
+      <c r="AH6" s="9"/>
+      <c r="AI6" s="9"/>
       <c r="AJ6" s="9"/>
       <c r="AK6" s="9"/>
-      <c r="AL6" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="AM6" s="28"/>
-      <c r="AN6" s="28"/>
-      <c r="AO6" s="28"/>
-      <c r="AP6" s="29"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
       <c r="AQ6" s="9"/>
       <c r="AR6" s="9"/>
       <c r="AS6" s="9"/>
@@ -1270,15 +1172,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="AL3:AU5"/>
-    <mergeCell ref="AL6:AP6"/>
-    <mergeCell ref="S4:AI4"/>
-    <mergeCell ref="Q6:AA6"/>
-    <mergeCell ref="AB6:AI6"/>
-    <mergeCell ref="N5:Z5"/>
-    <mergeCell ref="AA5:AI5"/>
-    <mergeCell ref="S3:AI3"/>
+  <mergeCells count="3">
+    <mergeCell ref="N6:AB6"/>
+    <mergeCell ref="N5:AB5"/>
+    <mergeCell ref="N3:AB4"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1287,15 +1184,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
@@ -1306,7 +1194,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -1501,15 +1389,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1520,7 +1409,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1537,4 +1426,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/スケジュール.xlsx
+++ b/スケジュール.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\川上 紗英\チーム制作\GameProductionPractice1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2590345_黒沢爽次\チーム制作\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687086A4-E66A-400C-9910-B253611BEC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946BA88B-5436-460C-BF68-6F07941580AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="-12525" windowWidth="21600" windowHeight="11295" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="5775" yWindow="-12240" windowWidth="21600" windowHeight="11370" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>2月</t>
     <rPh sb="1" eb="2">
@@ -81,23 +81,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>マップ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>タイトル、オプション、セーブ、ロード画面、敵の動き</t>
-    <rPh sb="18" eb="20">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ウゴ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>プレイヤーの動き</t>
     <rPh sb="6" eb="7">
       <t>ウゴ</t>
@@ -111,6 +94,52 @@
     </rPh>
     <rPh sb="1" eb="2">
       <t>ノ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ギミック</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮マップ</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>不具合修正</t>
+    <rPh sb="0" eb="3">
+      <t>フグアイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>マップ制作</t>
+    <rPh sb="3" eb="5">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サウンド、画像</t>
+    <rPh sb="5" eb="7">
+      <t>ガゾウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -174,7 +203,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -324,13 +353,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -373,26 +420,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -920,42 +1015,44 @@
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
-      <c r="N3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
-      <c r="T3" s="16"/>
-      <c r="U3" s="16"/>
-      <c r="V3" s="16"/>
-      <c r="W3" s="16"/>
-      <c r="X3" s="16"/>
-      <c r="Y3" s="16"/>
-      <c r="Z3" s="16"/>
-      <c r="AA3" s="16"/>
-      <c r="AB3" s="17"/>
-      <c r="AC3" s="9"/>
-      <c r="AD3" s="9"/>
-      <c r="AE3" s="9"/>
-      <c r="AF3" s="9"/>
-      <c r="AG3" s="9"/>
-      <c r="AH3" s="9"/>
-      <c r="AI3" s="9"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
+      <c r="W3" s="33"/>
+      <c r="X3" s="33"/>
+      <c r="Y3" s="33"/>
+      <c r="Z3" s="33"/>
+      <c r="AA3" s="33"/>
+      <c r="AB3" s="33"/>
+      <c r="AC3" s="33"/>
+      <c r="AD3" s="33"/>
+      <c r="AE3" s="33"/>
+      <c r="AF3" s="33"/>
+      <c r="AG3" s="33"/>
+      <c r="AH3" s="33"/>
+      <c r="AI3" s="34"/>
       <c r="AJ3" s="9"/>
       <c r="AK3" s="9"/>
-      <c r="AL3" s="9"/>
-      <c r="AM3" s="9"/>
-      <c r="AN3" s="9"/>
-      <c r="AO3" s="9"/>
-      <c r="AP3" s="9"/>
-      <c r="AQ3" s="9"/>
-      <c r="AR3" s="9"/>
-      <c r="AS3" s="9"/>
-      <c r="AT3" s="9"/>
-      <c r="AU3" s="9"/>
+      <c r="AL3" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM3" s="19"/>
+      <c r="AN3" s="19"/>
+      <c r="AO3" s="19"/>
+      <c r="AP3" s="19"/>
+      <c r="AQ3" s="19"/>
+      <c r="AR3" s="19"/>
+      <c r="AS3" s="19"/>
+      <c r="AT3" s="19"/>
+      <c r="AU3" s="20"/>
       <c r="AV3" s="9"/>
       <c r="AW3" s="9"/>
       <c r="AX3" s="9"/>
@@ -972,7 +1069,7 @@
     </row>
     <row r="4" spans="1:60" s="10" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -986,40 +1083,42 @@
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="20"/>
-      <c r="AC4" s="9"/>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="9"/>
-      <c r="AF4" s="9"/>
-      <c r="AG4" s="9"/>
-      <c r="AH4" s="9"/>
-      <c r="AI4" s="9"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+      <c r="X4" s="35"/>
+      <c r="Y4" s="35"/>
+      <c r="Z4" s="35"/>
+      <c r="AA4" s="35"/>
+      <c r="AB4" s="35"/>
+      <c r="AC4" s="35"/>
+      <c r="AD4" s="35"/>
+      <c r="AE4" s="35"/>
+      <c r="AF4" s="35"/>
+      <c r="AG4" s="35"/>
+      <c r="AH4" s="35"/>
+      <c r="AI4" s="36"/>
       <c r="AJ4" s="9"/>
       <c r="AK4" s="9"/>
-      <c r="AL4" s="9"/>
-      <c r="AM4" s="9"/>
-      <c r="AN4" s="9"/>
-      <c r="AO4" s="9"/>
-      <c r="AP4" s="9"/>
-      <c r="AQ4" s="9"/>
-      <c r="AR4" s="9"/>
-      <c r="AS4" s="9"/>
-      <c r="AT4" s="9"/>
-      <c r="AU4" s="9"/>
+      <c r="AL4" s="21"/>
+      <c r="AM4" s="22"/>
+      <c r="AN4" s="22"/>
+      <c r="AO4" s="22"/>
+      <c r="AP4" s="22"/>
+      <c r="AQ4" s="22"/>
+      <c r="AR4" s="22"/>
+      <c r="AS4" s="22"/>
+      <c r="AT4" s="22"/>
+      <c r="AU4" s="23"/>
       <c r="AV4" s="9"/>
       <c r="AW4" s="9"/>
       <c r="AX4" s="9"/>
@@ -1050,42 +1149,46 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
-      <c r="N5" s="12" t="s">
+      <c r="N5" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="30"/>
+      <c r="AA5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="9"/>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="9"/>
-      <c r="AF5" s="9"/>
-      <c r="AG5" s="9"/>
-      <c r="AH5" s="9"/>
-      <c r="AI5" s="9"/>
+      <c r="AB5" s="30"/>
+      <c r="AC5" s="30"/>
+      <c r="AD5" s="30"/>
+      <c r="AE5" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF5" s="30"/>
+      <c r="AG5" s="30"/>
+      <c r="AH5" s="30"/>
+      <c r="AI5" s="31"/>
       <c r="AJ5" s="9"/>
       <c r="AK5" s="9"/>
-      <c r="AL5" s="9"/>
-      <c r="AM5" s="9"/>
-      <c r="AN5" s="9"/>
-      <c r="AO5" s="9"/>
-      <c r="AP5" s="9"/>
-      <c r="AQ5" s="9"/>
-      <c r="AR5" s="9"/>
-      <c r="AS5" s="9"/>
-      <c r="AT5" s="9"/>
-      <c r="AU5" s="9"/>
+      <c r="AL5" s="24"/>
+      <c r="AM5" s="25"/>
+      <c r="AN5" s="25"/>
+      <c r="AO5" s="25"/>
+      <c r="AP5" s="25"/>
+      <c r="AQ5" s="25"/>
+      <c r="AR5" s="25"/>
+      <c r="AS5" s="25"/>
+      <c r="AT5" s="25"/>
+      <c r="AU5" s="26"/>
       <c r="AV5" s="9"/>
       <c r="AW5" s="9"/>
       <c r="AX5" s="9"/>
@@ -1116,37 +1219,41 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
-      <c r="N6" s="12" t="s">
-        <v>6</v>
-      </c>
+      <c r="N6" s="12"/>
       <c r="O6" s="13"/>
       <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
-      <c r="AF6" s="9"/>
-      <c r="AG6" s="9"/>
-      <c r="AH6" s="9"/>
-      <c r="AI6" s="9"/>
+      <c r="Q6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC6" s="30"/>
+      <c r="AD6" s="30"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="30"/>
+      <c r="AG6" s="30"/>
+      <c r="AH6" s="30"/>
+      <c r="AI6" s="31"/>
       <c r="AJ6" s="9"/>
       <c r="AK6" s="9"/>
-      <c r="AL6" s="9"/>
-      <c r="AM6" s="9"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="9"/>
-      <c r="AP6" s="9"/>
+      <c r="AL6" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="29"/>
       <c r="AQ6" s="9"/>
       <c r="AR6" s="9"/>
       <c r="AS6" s="9"/>
@@ -1172,10 +1279,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="N6:AB6"/>
-    <mergeCell ref="N5:AB5"/>
-    <mergeCell ref="N3:AB4"/>
+  <mergeCells count="9">
+    <mergeCell ref="AL3:AU5"/>
+    <mergeCell ref="AL6:AP6"/>
+    <mergeCell ref="S4:AI4"/>
+    <mergeCell ref="Q6:AA6"/>
+    <mergeCell ref="AB6:AI6"/>
+    <mergeCell ref="N5:Z5"/>
+    <mergeCell ref="S3:AI3"/>
+    <mergeCell ref="AA5:AD5"/>
+    <mergeCell ref="AE5:AI5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1195,6 +1308,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -1389,15 +1511,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
   <ds:schemaRefs>
@@ -1410,6 +1523,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1426,12 +1547,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>